--- a/data/data_raw/eurostat/AT_pig_population_apro_mt_lspig.xlsx
+++ b/data/data_raw/eurostat/AT_pig_population_apro_mt_lspig.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO15"/>
+  <dimension ref="A1:AP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +627,11 @@
       <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -756,6 +761,7 @@
       <c r="AO2" t="n">
         <v>2534.44</v>
       </c>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -887,6 +893,7 @@
       <c r="AO3" t="n">
         <v>614.53</v>
       </c>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1014,6 +1021,7 @@
       <c r="AO4" t="n">
         <v>204.57</v>
       </c>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1141,6 +1149,7 @@
       <c r="AO5" t="n">
         <v>201.37</v>
       </c>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1272,6 +1281,7 @@
       <c r="AO6" t="n">
         <v>139.67</v>
       </c>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1399,6 +1409,7 @@
       <c r="AO7" t="n">
         <v>19.75</v>
       </c>
+      <c r="AP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1526,6 +1537,7 @@
       <c r="AO8" t="n">
         <v>61.7</v>
       </c>
+      <c r="AP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1653,6 +1665,7 @@
       <c r="AO9" t="n">
         <v>21.25</v>
       </c>
+      <c r="AP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1780,6 +1793,7 @@
       <c r="AO10" t="n">
         <v>627.5599999999999</v>
       </c>
+      <c r="AP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1907,6 +1921,7 @@
       <c r="AO11" t="n">
         <v>1087.78</v>
       </c>
+      <c r="AP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -2034,6 +2049,7 @@
       <c r="AO12" t="n">
         <v>512.7</v>
       </c>
+      <c r="AP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2161,6 +2177,7 @@
       <c r="AO13" t="n">
         <v>441.68</v>
       </c>
+      <c r="AP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2288,6 +2305,7 @@
       <c r="AO14" t="n">
         <v>133.4</v>
       </c>
+      <c r="AP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2419,6 +2437,7 @@
       <c r="AO15" t="n">
         <v>3.2</v>
       </c>
+      <c r="AP15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
